--- a/artfynd/A 6235-2023 artfynd.xlsx
+++ b/artfynd/A 6235-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116527871</v>
+        <v>116528273</v>
       </c>
       <c r="B2" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576572</v>
+        <v>576550</v>
       </c>
       <c r="R2" t="n">
-        <v>7059575</v>
+        <v>7059597</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116528273</v>
+        <v>116525018</v>
       </c>
       <c r="B3" t="n">
-        <v>90438</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576550</v>
+        <v>576582</v>
       </c>
       <c r="R3" t="n">
-        <v>7059597</v>
+        <v>7059672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,27 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116528105</v>
+        <v>116527791</v>
       </c>
       <c r="B4" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576569</v>
+        <v>576552</v>
       </c>
       <c r="R4" t="n">
-        <v>7059567</v>
+        <v>7059577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116528020</v>
+        <v>116525974</v>
       </c>
       <c r="B5" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576562</v>
+        <v>576572</v>
       </c>
       <c r="R5" t="n">
-        <v>7059575</v>
+        <v>7059682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,67 +1091,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116528129</v>
+        <v>116527570</v>
       </c>
       <c r="B6" t="n">
-        <v>56490</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodtjärnsbäcken (Bodtjärnsbäcken), Ång</t>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576566</v>
+        <v>576589</v>
       </c>
       <c r="R6" t="n">
-        <v>7059564</v>
+        <v>7059578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,15 +1203,463 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>116527871</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576572</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7059575</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116528020</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>576562</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7059575</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Kamilla Andersson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116528105</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576569</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7059567</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>116528129</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576566</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7059564</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6235-2023 artfynd.xlsx
+++ b/artfynd/A 6235-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116525018</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116525974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527570</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116527871</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528020</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528105</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,8 +1705,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116528129</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>